--- a/staff_thai_standard.xlsx
+++ b/staff_thai_standard.xlsx
@@ -1,22 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\evergreen\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA8B245-CFA3-421F-92E2-79BA5FAA64D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="รายชื่อพนักงาน" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="สรุปตาม License" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="สรุปโครงสร้างองค์กร" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="รายชื่อพนักงาน" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">รายชื่อพนักงาน!$A$1:$H$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">รายชื่อพนักงาน!$A$1:$H$86</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,177 +37,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="397">
-  <si>
-    <t xml:space="preserve">ชื่อ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นามสกุล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ชื่อเล่น</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แผนก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตำแหน่ง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ประเภท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email (@chhindustry.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แผนก (มาตรฐาน)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตำแหน่ง (มาตรฐาน)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แผนก (เดิม)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตำแหน่ง (เดิม)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไพโรจน์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พรมจีน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โรจน์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายการเงินและบัญชี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้จัดการฝ่ายการเงินและบัญชี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จงคม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รายเดือน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phairote.p@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting and Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting and Finance Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ภาวิตา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">คุ้มด้วง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่การเงินและบัญชี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pavita.a@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting and Finance Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พรพิมล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ดาวลอย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pornpimol.d@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ภัทรชนน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จันทะ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">กิ่ง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายการตลาด</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้จัดการฝ่ายการตลาด</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phattharachanon.c@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Marketing Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อาชวิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วาณิชวัฒนะสกุล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อดัม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่การตลาด</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adam.a@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ชนากานต์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ศิริแส</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ป๊อป</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chanakan.s@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ธมลวรรณ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ษัษฐชาคร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มิว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tamonwan.s@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุทัศน์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ใจเอี่ยม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตั้ม</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="377">
+  <si>
+    <t>ชื่อ</t>
+  </si>
+  <si>
+    <t>นามสกุล</t>
+  </si>
+  <si>
+    <t>ชื่อเล่น</t>
+  </si>
+  <si>
+    <t>แผนก</t>
+  </si>
+  <si>
+    <t>ตำแหน่ง</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>ประเภท</t>
+  </si>
+  <si>
+    <t>Email (@chhindustry.com)</t>
+  </si>
+  <si>
+    <t>แผนก (มาตรฐาน)</t>
+  </si>
+  <si>
+    <t>ตำแหน่ง (มาตรฐาน)</t>
+  </si>
+  <si>
+    <t>แผนก (เดิม)</t>
+  </si>
+  <si>
+    <t>ตำแหน่ง (เดิม)</t>
+  </si>
+  <si>
+    <t>ไพโรจน์</t>
+  </si>
+  <si>
+    <t>พรมจีน</t>
+  </si>
+  <si>
+    <t>โรจน์</t>
+  </si>
+  <si>
+    <t>ฝ่ายการเงินและบัญชี</t>
+  </si>
+  <si>
+    <t>ผู้จัดการฝ่ายการเงินและบัญชี</t>
+  </si>
+  <si>
+    <t>จงคม</t>
+  </si>
+  <si>
+    <t>รายเดือน</t>
+  </si>
+  <si>
+    <t>phairote.p@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Accounting and Finance</t>
+  </si>
+  <si>
+    <t>Accounting and Finance Manager</t>
+  </si>
+  <si>
+    <t>ภาวิตา</t>
+  </si>
+  <si>
+    <t>คุ้มด้วง</t>
+  </si>
+  <si>
+    <t>อัน</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่การเงินและบัญชี</t>
+  </si>
+  <si>
+    <t>pavita.a@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Accounting and Finance Officer</t>
+  </si>
+  <si>
+    <t>พรพิมล</t>
+  </si>
+  <si>
+    <t>ดาวลอย</t>
+  </si>
+  <si>
+    <t>มล</t>
+  </si>
+  <si>
+    <t>pornpimol.d@chhindustry.com</t>
+  </si>
+  <si>
+    <t>ภัทรชนน</t>
+  </si>
+  <si>
+    <t>จันทะ</t>
+  </si>
+  <si>
+    <t>กิ่ง</t>
+  </si>
+  <si>
+    <t>ฝ่ายการตลาด</t>
+  </si>
+  <si>
+    <t>ผู้จัดการฝ่ายการตลาด</t>
+  </si>
+  <si>
+    <t>phattharachanon.c@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Digital Marketing</t>
+  </si>
+  <si>
+    <t>Digital Marketing Manager</t>
+  </si>
+  <si>
+    <t>อาชวิน</t>
+  </si>
+  <si>
+    <t>วาณิชวัฒนะสกุล</t>
+  </si>
+  <si>
+    <t>อดัม</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่การตลาด</t>
+  </si>
+  <si>
+    <t>adam.a@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Marketing Officer</t>
+  </si>
+  <si>
+    <t>ชนากานต์</t>
+  </si>
+  <si>
+    <t>ศิริแส</t>
+  </si>
+  <si>
+    <t>ป๊อป</t>
+  </si>
+  <si>
+    <t>chanakan.s@chhindustry.com</t>
+  </si>
+  <si>
+    <t>ธมลวรรณ</t>
+  </si>
+  <si>
+    <t>ษัษฐชาคร</t>
+  </si>
+  <si>
+    <t>มิว</t>
+  </si>
+  <si>
+    <t>tamonwan.s@chhindustry.com</t>
+  </si>
+  <si>
+    <t>สุทัศน์</t>
+  </si>
+  <si>
+    <t>ใจเอี่ยม</t>
+  </si>
+  <si>
+    <t>ตั้ม</t>
   </si>
   <si>
     <r>
@@ -215,7 +227,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(CAD/CNC)</t>
+      <t>(CAD/CNC)</t>
     </r>
   </si>
   <si>
@@ -236,35 +248,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CAD/CNC</t>
+      <t>CAD/CNC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">วชิรศักดิ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sutad.j@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายวิศวกรรม (CAD/CNC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้างาน CAD/CNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing and CNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing and CNC Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รัฐศาสตร์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แสงสุวรรณ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปิ๊ง</t>
+    <t>วชิรศักดิ์</t>
+  </si>
+  <si>
+    <t>sutad.j@chhindustry.com</t>
+  </si>
+  <si>
+    <t>ฝ่ายวิศวกรรม (CAD/CNC)</t>
+  </si>
+  <si>
+    <t>หัวหน้างาน CAD/CNC</t>
+  </si>
+  <si>
+    <t>Drawing and CNC</t>
+  </si>
+  <si>
+    <t>Drawing and CNC Supervisor</t>
+  </si>
+  <si>
+    <t>รัฐศาสตร์</t>
+  </si>
+  <si>
+    <t>แสงสุวรรณ์</t>
+  </si>
+  <si>
+    <t>ปิ๊ง</t>
   </si>
   <si>
     <r>
@@ -284,26 +296,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CAD/CNC</t>
+      <t>CAD/CNC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ratthasat.s@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่ CAD/CNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing and CNC Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khaing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โซข่าย</t>
+    <t>ratthasat.s@chhindustry.com</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่ CAD/CNC</t>
+  </si>
+  <si>
+    <t>Drawing and CNC Officer</t>
+  </si>
+  <si>
+    <t>Soe</t>
+  </si>
+  <si>
+    <t>Khaing</t>
+  </si>
+  <si>
+    <t>โซข่าย</t>
   </si>
   <si>
     <r>
@@ -323,194 +335,194 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CAD/CNC</t>
+      <t>CAD/CNC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">รายวัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ช่างเทคนิค CAD/CNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drawing and CNC Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อองตู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุเมธ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นุ่มทอง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ต้น</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายทรัพยากรบุคคล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่ทรัพยากรบุคคล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sumeth.n@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Resources Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นันทา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นิ่มนวล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แหม่ม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้ช่วยฝ่ายทรัพยากรบุคคล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Resources Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปาณัสม์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เตียวนะ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ก้าน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายเทคโนโลยีสารสนเทศ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่เทคโนโลยีสารสนเทศ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">panut.t@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ภาณุวัต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แจ้งชัดใจ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อิ๊น</t>
-  </si>
-  <si>
-    <t xml:space="preserve">panuwat.j@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วิภวา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จันทร์แสงวัฒนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฟิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wipawa.c@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ขวัญชัย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">กลิ่นประทุม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายซ่อมบำรุง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้างานซ่อมบำรุง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kwanchai.k@chhindustry.com</t>
+    <t>รายวัน</t>
+  </si>
+  <si>
+    <t>ช่างเทคนิค CAD/CNC</t>
+  </si>
+  <si>
+    <t>Drawing and CNC Staff</t>
+  </si>
+  <si>
+    <t>Aung</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>อองตู</t>
+  </si>
+  <si>
+    <t>สุเมธ</t>
+  </si>
+  <si>
+    <t>นุ่มทอง</t>
+  </si>
+  <si>
+    <t>ต้น</t>
+  </si>
+  <si>
+    <t>ฝ่ายทรัพยากรบุคคล</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่ทรัพยากรบุคคล</t>
+  </si>
+  <si>
+    <t>sumeth.n@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Human resources</t>
+  </si>
+  <si>
+    <t>Human Resources Officer</t>
+  </si>
+  <si>
+    <t>นันทา</t>
+  </si>
+  <si>
+    <t>นิ่มนวล</t>
+  </si>
+  <si>
+    <t>แหม่ม</t>
+  </si>
+  <si>
+    <t>ผู้ช่วยฝ่ายทรัพยากรบุคคล</t>
+  </si>
+  <si>
+    <t>Human Resources Staff</t>
+  </si>
+  <si>
+    <t>ปาณัสม์</t>
+  </si>
+  <si>
+    <t>เตียวนะ</t>
+  </si>
+  <si>
+    <t>ก้าน</t>
+  </si>
+  <si>
+    <t>ฝ่ายเทคโนโลยีสารสนเทศ</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่เทคโนโลยีสารสนเทศ</t>
+  </si>
+  <si>
+    <t>panut.t@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Information Technology Office</t>
+  </si>
+  <si>
+    <t>ภาณุวัต</t>
+  </si>
+  <si>
+    <t>แจ้งชัดใจ</t>
+  </si>
+  <si>
+    <t>อิ๊น</t>
+  </si>
+  <si>
+    <t>panuwat.j@chhindustry.com</t>
+  </si>
+  <si>
+    <t>วิภวา</t>
+  </si>
+  <si>
+    <t>จันทร์แสงวัฒนา</t>
+  </si>
+  <si>
+    <t>ฟิน</t>
+  </si>
+  <si>
+    <t>wipawa.c@chhindustry.com</t>
+  </si>
+  <si>
+    <t>ขวัญชัย</t>
+  </si>
+  <si>
+    <t>กลิ่นประทุม</t>
+  </si>
+  <si>
+    <t>ผา</t>
+  </si>
+  <si>
+    <t>ฝ่ายซ่อมบำรุง</t>
+  </si>
+  <si>
+    <t>หัวหน้างานซ่อมบำรุง</t>
+  </si>
+  <si>
+    <t>kwanchai.k@chhindustry.com</t>
   </si>
   <si>
     <t xml:space="preserve">Maintenance </t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ชูชัยศรี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้บริหาร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">กรรมการผู้จัดการ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jongkhom.c@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Managing Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พึ่งอัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้จัดการฝ่ายผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wachirasak.p@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">กันตพัฒน์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตรีพิริยะมงคล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปลั๊ก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้ช่วยผู้จัดการฝ่ายผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guntaphat.t@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistant Production Manager</t>
+    <t>Maintenance Supervisor</t>
+  </si>
+  <si>
+    <t>ชูชัยศรี</t>
+  </si>
+  <si>
+    <t>จง</t>
+  </si>
+  <si>
+    <t>ผู้บริหาร</t>
+  </si>
+  <si>
+    <t>กรรมการผู้จัดการ</t>
+  </si>
+  <si>
+    <t>jongkhom.c@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>พึ่งอัน</t>
+  </si>
+  <si>
+    <t>ฝ่ายผลิต</t>
+  </si>
+  <si>
+    <t>ผู้จัดการฝ่ายผลิต</t>
+  </si>
+  <si>
+    <t>wachirasak.p@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Production Manager</t>
+  </si>
+  <si>
+    <t>กันตพัฒน์</t>
+  </si>
+  <si>
+    <t>ตรีพิริยะมงคล</t>
+  </si>
+  <si>
+    <t>ปลั๊ก</t>
+  </si>
+  <si>
+    <t>ผู้ช่วยผู้จัดการฝ่ายผลิต</t>
+  </si>
+  <si>
+    <t>guntaphat.t@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Assistant Production Manager</t>
   </si>
   <si>
     <r>
@@ -521,7 +533,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">N</t>
+      <t>N</t>
     </r>
     <r>
       <rPr>
@@ -530,14 +542,14 @@
         <rFont val="FreeSans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">น</t>
+      <t>น</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Zin Tun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ทน</t>
+    <t>Zin Tun</t>
+  </si>
+  <si>
+    <t>ทน</t>
   </si>
   <si>
     <r>
@@ -557,95 +569,95 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">WPC</t>
+      <t>WPC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">พนักงานผลิต WPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production WPC Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เซียง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โก อู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เซียงโกอู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Htet Oo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หลิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไม่มีนามสกุล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyaw Kyow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โจ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พนักงานผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซอซอ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พัชรี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขพลอย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ย๊ะ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่ธุรการฝ่ายผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phatcharee.s@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Administrative Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อมรเทพ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นพศรี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โอม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้ช่วยหัวหน้างานผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amorntep.n@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistant Production Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thein</t>
+    <t>พนักงานผลิต WPC</t>
+  </si>
+  <si>
+    <t>Production WPC Staff</t>
+  </si>
+  <si>
+    <t>เซียง</t>
+  </si>
+  <si>
+    <t>โก อู</t>
+  </si>
+  <si>
+    <t>เซียงโกอู</t>
+  </si>
+  <si>
+    <t>Htet Oo</t>
+  </si>
+  <si>
+    <t>อู</t>
+  </si>
+  <si>
+    <t>Tin</t>
+  </si>
+  <si>
+    <t>หลิน</t>
+  </si>
+  <si>
+    <t>ไม่มีนามสกุล</t>
+  </si>
+  <si>
+    <t>Kyaw Kyow</t>
+  </si>
+  <si>
+    <t>โจ</t>
+  </si>
+  <si>
+    <t>พนักงานผลิต</t>
+  </si>
+  <si>
+    <t>Production Staff</t>
+  </si>
+  <si>
+    <t>Zaw</t>
+  </si>
+  <si>
+    <t>ซอซอ</t>
+  </si>
+  <si>
+    <t>พัชรี</t>
+  </si>
+  <si>
+    <t>สุขพลอย</t>
+  </si>
+  <si>
+    <t>ย๊ะ</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่ธุรการฝ่ายผลิต</t>
+  </si>
+  <si>
+    <t>phatcharee.s@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Production Administrative Officer</t>
+  </si>
+  <si>
+    <t>อมรเทพ</t>
+  </si>
+  <si>
+    <t>นพศรี</t>
+  </si>
+  <si>
+    <t>โอม</t>
+  </si>
+  <si>
+    <t>ผู้ช่วยหัวหน้างานผลิต</t>
+  </si>
+  <si>
+    <t>amorntep.n@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Assistant Production Supervisor</t>
+  </si>
+  <si>
+    <t>Thein</t>
   </si>
   <si>
     <r>
@@ -665,80 +677,80 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(CM12)</t>
+      <t>(CM12)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">พนักงานพ่นสี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พยุง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Spray Painting Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar Aung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซิมยา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaw Htay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มีซอ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ขาวกลาง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ทอง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้ากลุ่มงานพ่นสี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Spray Painting Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maung Htay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phyo Lin Htet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อองเพียว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ko Ko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มินโก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chit Aung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เพียวชิด</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tun</t>
+    <t>พนักงานพ่นสี</t>
+  </si>
+  <si>
+    <t>พยุง</t>
+  </si>
+  <si>
+    <t>Production Spray Painting Staff</t>
+  </si>
+  <si>
+    <t>Yin</t>
+  </si>
+  <si>
+    <t>Mar Aung</t>
+  </si>
+  <si>
+    <t>ซิมยา</t>
+  </si>
+  <si>
+    <t>Mee</t>
+  </si>
+  <si>
+    <t>Zaw Htay</t>
+  </si>
+  <si>
+    <t>มีซอ</t>
+  </si>
+  <si>
+    <t>ขาวกลาง</t>
+  </si>
+  <si>
+    <t>ทอง</t>
+  </si>
+  <si>
+    <t>หัวหน้ากลุ่มงานพ่นสี</t>
+  </si>
+  <si>
+    <t>Production Spray Painting Leader</t>
+  </si>
+  <si>
+    <t>Maung Htay</t>
+  </si>
+  <si>
+    <t>เท</t>
+  </si>
+  <si>
+    <t>Phyo Lin Htet</t>
+  </si>
+  <si>
+    <t>อองเพียว</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Ko Ko</t>
+  </si>
+  <si>
+    <t>มินโก</t>
+  </si>
+  <si>
+    <t>Phyo</t>
+  </si>
+  <si>
+    <t>Chit Aung</t>
+  </si>
+  <si>
+    <t>เพียวชิด</t>
+  </si>
+  <si>
+    <t>Tun</t>
   </si>
   <si>
     <r>
@@ -758,7 +770,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(CM06)</t>
+      <t>(CM06)</t>
     </r>
   </si>
   <si>
@@ -779,615 +791,552 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">WPC</t>
+      <t>WPC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">หัวหน้ากะผลิต WPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production WPC Shift Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โซวิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyaw Zin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myat Maung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตาว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lin Tun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เนย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi Wi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มีมีวิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lin Oo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เนยลิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Htet Aung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซอ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min Tun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ใช่</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Htay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซอเท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thet Paing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เพียวเทด</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hlaing Oo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซอเหลียง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Htay Win</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เทเท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seu Seu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เทซู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ko Oo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปลาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ลิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu Phyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ชู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สมพร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เรืองศรี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้ากลุ่มงานผลิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">somporn20021970@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Supervisor Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เพลินตา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วงศ์ประเสริฐ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายจัดซื้อ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่จัดซื้อ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plearnta.w@chhindustry.com</t>
+    <t>หัวหน้ากะผลิต WPC</t>
+  </si>
+  <si>
+    <t>Production WPC Shift Supervisor</t>
+  </si>
+  <si>
+    <t>Win</t>
+  </si>
+  <si>
+    <t>โซวิน</t>
+  </si>
+  <si>
+    <t>Sai</t>
+  </si>
+  <si>
+    <t>Kyaw Zin</t>
+  </si>
+  <si>
+    <t>ซิน</t>
+  </si>
+  <si>
+    <t>Kaung</t>
+  </si>
+  <si>
+    <t>Myat Maung</t>
+  </si>
+  <si>
+    <t>ตาว</t>
+  </si>
+  <si>
+    <t>Nay</t>
+  </si>
+  <si>
+    <t>Lin Tun</t>
+  </si>
+  <si>
+    <t>เนย</t>
+  </si>
+  <si>
+    <t>Mi</t>
+  </si>
+  <si>
+    <t>Mi Wi</t>
+  </si>
+  <si>
+    <t>มีมีวิน</t>
+  </si>
+  <si>
+    <t>Lin Oo</t>
+  </si>
+  <si>
+    <t>เนยลิน</t>
+  </si>
+  <si>
+    <t>Htet Aung</t>
+  </si>
+  <si>
+    <t>ซอ</t>
+  </si>
+  <si>
+    <t>Shin</t>
+  </si>
+  <si>
+    <t>Min Tun</t>
+  </si>
+  <si>
+    <t>ใช่</t>
+  </si>
+  <si>
+    <t>Saw</t>
+  </si>
+  <si>
+    <t>Htay</t>
+  </si>
+  <si>
+    <t>ซอเท</t>
+  </si>
+  <si>
+    <t>Thet Paing</t>
+  </si>
+  <si>
+    <t>เพียวเทด</t>
+  </si>
+  <si>
+    <t>Hlaing Oo</t>
+  </si>
+  <si>
+    <t>ซอเหลียง</t>
+  </si>
+  <si>
+    <t>Htay Win</t>
+  </si>
+  <si>
+    <t>เทเท</t>
+  </si>
+  <si>
+    <t>Thay</t>
+  </si>
+  <si>
+    <t>Seu Seu</t>
+  </si>
+  <si>
+    <t>เทซู</t>
+  </si>
+  <si>
+    <t>Moa</t>
+  </si>
+  <si>
+    <t>Ko Oo</t>
+  </si>
+  <si>
+    <t>ปลาย</t>
+  </si>
+  <si>
+    <t>Lin</t>
+  </si>
+  <si>
+    <t>ลิน</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Thu Phyo</t>
+  </si>
+  <si>
+    <t>ชู</t>
+  </si>
+  <si>
+    <t>สมพร</t>
+  </si>
+  <si>
+    <t>เรืองศรี</t>
+  </si>
+  <si>
+    <t>พร</t>
+  </si>
+  <si>
+    <t>หัวหน้ากลุ่มงานผลิต</t>
+  </si>
+  <si>
+    <t>somporn20021970@gmail.com</t>
+  </si>
+  <si>
+    <t>Production Supervisor Leader</t>
+  </si>
+  <si>
+    <t>เพลินตา</t>
+  </si>
+  <si>
+    <t>วงศ์ประเสริฐ</t>
+  </si>
+  <si>
+    <t>ตา</t>
+  </si>
+  <si>
+    <t>ฝ่ายจัดซื้อ</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่จัดซื้อ</t>
+  </si>
+  <si>
+    <t>plearnta.w@chhindustry.com</t>
   </si>
   <si>
     <t xml:space="preserve">Purchasing </t>
   </si>
   <si>
-    <t xml:space="preserve">Purchasing Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สมหมาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">บัวแย้ม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฉุย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายควบคุมคุณภาพและบรรจุภัณฑ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พนักงานควบคุมคุณภาพและบรรจุภัณฑ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality and Packing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality and Packing Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไค</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วิน ไม่มีนามสกุล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไควิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุเตียน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มามน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni Win</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min Hlaing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zi Ho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hnin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thwe Aye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มาลี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เทศแก้ว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ลี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thidar San</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เอ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้ากลุ่มงานควบคุมคุณภาพและบรรจุภัณฑ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พีระยุทธ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality and Packing Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เหมรัศมิ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วงศ์โพธิ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ต๊ะ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moment.ta.2409@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หม่องวิลัย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้างานควบคุมคุณภาพและบรรจุภัณฑ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peerayut.m@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality and Packing Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นวพล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ชูเกียรติ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เล็ก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายขาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้จัดการฝ่ายขาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nawapol.c@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พิชฌาภา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วัดอิ่ม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">คิว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่ขาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pitchapa.w@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ดวงมณี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ตั้งสุขศรี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เซิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">duangmanee.t@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปิยะพงศ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">วรรณภาพรรณ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แบงค์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">piyapong.w@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รัชพล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สังขวรรณ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เพ้นท์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ratchapol.s@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มัทนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">บานเย็น</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มัท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">muttana.b@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เกสรา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ภัทรนวงษ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เกด</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gassara.p@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อรวรรณ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อมรปิยะกิจ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เมย์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่ธุรการฝ่ายขาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orawan.a@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Administrative Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ธีรชัย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เมฆแก้ว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ต้อม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้ประสานงานฝ่ายขาย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">theerachai.mekkaew@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Coordinator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นลธวัช</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พรหมยิ้มแย้ม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ออม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ฝ่ายคลังสินค้าและโลจิสติกส์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พนักงานคลังสินค้าและโลจิสติกส์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จตุพร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warehouse and transportation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warehouse and transportation Staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaw Tun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">โทน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ธรรมนูญ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไชยแก้ว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นิน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaw Oo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซออู</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Than</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Htike Aung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แทะอ่าว</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อนุสรณ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ยิ้มดี</t>
-  </si>
-  <si>
-    <t xml:space="preserve">นุ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khant Kyaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มินคัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyaw Htwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จอ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปาน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ออระอ่อน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ทองงาม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไก่</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้างานคลังสินค้าและโลจิสติกส์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jatuporn.t@chhindustry.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warehouse and Logistics Supervisor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M365 License Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">License Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จำนวน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Standard + D365 BC Premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Standard + Power BI Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Basic + D365 BC Team Members</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Basic + D365 BC Premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Business Standard + D365 BC Premium + Power BI Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Fabric (Free) only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไม่มี Email (รายวัน/ไม่มี account)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ระดับ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">จำนวน (คน)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้บริหารระดับสูง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้บริหารระดับกลาง</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เจ้าหน้าที่</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปฏิบัติการ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">หัวหน้างาน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รวมทั้งหมด</t>
+    <t>Purchasing Officer</t>
+  </si>
+  <si>
+    <t>สมหมาย</t>
+  </si>
+  <si>
+    <t>บัวแย้ม</t>
+  </si>
+  <si>
+    <t>ฉุย</t>
+  </si>
+  <si>
+    <t>ฝ่ายควบคุมคุณภาพและบรรจุภัณฑ์</t>
+  </si>
+  <si>
+    <t>พนักงานควบคุมคุณภาพและบรรจุภัณฑ์</t>
+  </si>
+  <si>
+    <t>Aye</t>
+  </si>
+  <si>
+    <t>Quality and Packing</t>
+  </si>
+  <si>
+    <t>Quality and Packing Staff</t>
+  </si>
+  <si>
+    <t>ไค</t>
+  </si>
+  <si>
+    <t>วิน ไม่มีนามสกุล</t>
+  </si>
+  <si>
+    <t>ไควิน</t>
+  </si>
+  <si>
+    <t>สุเตียน</t>
+  </si>
+  <si>
+    <t>Ma</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>มามน</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <t>Ni Win</t>
+  </si>
+  <si>
+    <t>นี</t>
+  </si>
+  <si>
+    <t>Zin</t>
+  </si>
+  <si>
+    <t>Min Hlaing</t>
+  </si>
+  <si>
+    <t>Zar</t>
+  </si>
+  <si>
+    <t>Zi Ho</t>
+  </si>
+  <si>
+    <t>ซา</t>
+  </si>
+  <si>
+    <t>Hnin</t>
+  </si>
+  <si>
+    <t>Thwe Aye</t>
+  </si>
+  <si>
+    <t>มาลี</t>
+  </si>
+  <si>
+    <t>เทศแก้ว</t>
+  </si>
+  <si>
+    <t>ลี</t>
+  </si>
+  <si>
+    <t>Thidar San</t>
+  </si>
+  <si>
+    <t>เอ</t>
+  </si>
+  <si>
+    <t>หัวหน้ากลุ่มงานควบคุมคุณภาพและบรรจุภัณฑ์</t>
+  </si>
+  <si>
+    <t>พีระยุทธ</t>
+  </si>
+  <si>
+    <t>Quality and Packing Leader</t>
+  </si>
+  <si>
+    <t>เหมรัศมิ์</t>
+  </si>
+  <si>
+    <t>วงศ์โพธิ์</t>
+  </si>
+  <si>
+    <t>ต๊ะ</t>
+  </si>
+  <si>
+    <t>moment.ta.2409@gmail.com</t>
+  </si>
+  <si>
+    <t>หม่องวิลัย</t>
+  </si>
+  <si>
+    <t>พี</t>
+  </si>
+  <si>
+    <t>หัวหน้างานควบคุมคุณภาพและบรรจุภัณฑ์</t>
+  </si>
+  <si>
+    <t>peerayut.m@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Quality and Packing Supervisor</t>
+  </si>
+  <si>
+    <t>นวพล</t>
+  </si>
+  <si>
+    <t>ชูเกียรติ</t>
+  </si>
+  <si>
+    <t>เล็ก</t>
+  </si>
+  <si>
+    <t>ฝ่ายขาย</t>
+  </si>
+  <si>
+    <t>ผู้จัดการฝ่ายขาย</t>
+  </si>
+  <si>
+    <t>nawapol.c@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Sales Manager</t>
+  </si>
+  <si>
+    <t>พิชฌาภา</t>
+  </si>
+  <si>
+    <t>วัดอิ่ม</t>
+  </si>
+  <si>
+    <t>คิว</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่ขาย</t>
+  </si>
+  <si>
+    <t>pitchapa.w@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Sales Officer</t>
+  </si>
+  <si>
+    <t>ดวงมณี</t>
+  </si>
+  <si>
+    <t>ตั้งสุขศรี</t>
+  </si>
+  <si>
+    <t>เซิน</t>
+  </si>
+  <si>
+    <t>duangmanee.t@chhindustry.com</t>
+  </si>
+  <si>
+    <t>ปิยะพงศ์</t>
+  </si>
+  <si>
+    <t>วรรณภาพรรณ์</t>
+  </si>
+  <si>
+    <t>แบงค์</t>
+  </si>
+  <si>
+    <t>piyapong.w@chhindustry.com</t>
+  </si>
+  <si>
+    <t>รัชพล</t>
+  </si>
+  <si>
+    <t>สังขวรรณ</t>
+  </si>
+  <si>
+    <t>เพ้นท์</t>
+  </si>
+  <si>
+    <t>ratchapol.s@chhindustry.com</t>
+  </si>
+  <si>
+    <t>มัทนา</t>
+  </si>
+  <si>
+    <t>บานเย็น</t>
+  </si>
+  <si>
+    <t>มัท</t>
+  </si>
+  <si>
+    <t>muttana.b@chhindustry.com</t>
+  </si>
+  <si>
+    <t>เกสรา</t>
+  </si>
+  <si>
+    <t>ภัทรนวงษ์</t>
+  </si>
+  <si>
+    <t>เกด</t>
+  </si>
+  <si>
+    <t>gassara.p@chhindustry.com</t>
+  </si>
+  <si>
+    <t>อรวรรณ</t>
+  </si>
+  <si>
+    <t>อมรปิยะกิจ</t>
+  </si>
+  <si>
+    <t>เมย์</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่ธุรการฝ่ายขาย</t>
+  </si>
+  <si>
+    <t>orawan.a@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Sales Administrative Officer</t>
+  </si>
+  <si>
+    <t>ธีรชัย</t>
+  </si>
+  <si>
+    <t>เมฆแก้ว</t>
+  </si>
+  <si>
+    <t>ต้อม</t>
+  </si>
+  <si>
+    <t>ผู้ประสานงานฝ่ายขาย</t>
+  </si>
+  <si>
+    <t>theerachai.mekkaew@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Sales Coordinator</t>
+  </si>
+  <si>
+    <t>นลธวัช</t>
+  </si>
+  <si>
+    <t>พรหมยิ้มแย้ม</t>
+  </si>
+  <si>
+    <t>ออม</t>
+  </si>
+  <si>
+    <t>ฝ่ายคลังสินค้าและโลจิสติกส์</t>
+  </si>
+  <si>
+    <t>พนักงานคลังสินค้าและโลจิสติกส์</t>
+  </si>
+  <si>
+    <t>จตุพร</t>
+  </si>
+  <si>
+    <t>Warehouse and transportation</t>
+  </si>
+  <si>
+    <t>Warehouse and transportation Staff</t>
+  </si>
+  <si>
+    <t>Zaw Tun</t>
+  </si>
+  <si>
+    <t>โทน</t>
+  </si>
+  <si>
+    <t>ธรรมนูญ</t>
+  </si>
+  <si>
+    <t>ไชยแก้ว</t>
+  </si>
+  <si>
+    <t>นิน</t>
+  </si>
+  <si>
+    <t>Naing</t>
+  </si>
+  <si>
+    <t>Zaw Oo</t>
+  </si>
+  <si>
+    <t>ซออู</t>
+  </si>
+  <si>
+    <t>Than</t>
+  </si>
+  <si>
+    <t>Htike Aung</t>
+  </si>
+  <si>
+    <t>แทะอ่าว</t>
+  </si>
+  <si>
+    <t>อนุสรณ์</t>
+  </si>
+  <si>
+    <t>ยิ้มดี</t>
+  </si>
+  <si>
+    <t>นุ</t>
+  </si>
+  <si>
+    <t>Khant Kyaw</t>
+  </si>
+  <si>
+    <t>มินคัน</t>
+  </si>
+  <si>
+    <t>Kyaw</t>
+  </si>
+  <si>
+    <t>Kyaw Htwe</t>
+  </si>
+  <si>
+    <t>จอ</t>
+  </si>
+  <si>
+    <t>ปาน</t>
+  </si>
+  <si>
+    <t>ออระอ่อน</t>
+  </si>
+  <si>
+    <t>ทองงาม</t>
+  </si>
+  <si>
+    <t>ไก่</t>
+  </si>
+  <si>
+    <t>หัวหน้างานคลังสินค้าและโลจิสติกส์</t>
+  </si>
+  <si>
+    <t>jatuporn.t@chhindustry.com</t>
+  </si>
+  <si>
+    <t>Warehouse and Logistics Supervisor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1396,26 +1345,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1427,35 +1360,18 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1468,188 +1384,53 @@
         <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
-        <bgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4472C4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1708,51 +1489,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5496"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1760,12 +1553,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1794,7 +1587,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1815,7 +1608,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1866,7 +1659,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1884,34 +1677,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L87"/>
-  <sheetFormatPr defaultColWidth="30.13671875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="30.1328125" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="35"/>
+    <col min="1" max="1" width="8.73046875" customWidth="1"/>
+    <col min="2" max="2" width="14.06640625" customWidth="1"/>
+    <col min="3" max="3" width="12.73046875" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1949,7 +1741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1987,7 +1779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -2025,7 +1817,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -2063,7 +1855,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -2101,7 +1893,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -2139,7 +1931,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
@@ -2177,7 +1969,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
@@ -2215,7 +2007,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
@@ -2253,7 +2045,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
         <v>65</v>
       </c>
@@ -2291,7 +2083,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
         <v>72</v>
       </c>
@@ -2327,7 +2119,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
         <v>79</v>
       </c>
@@ -2363,7 +2155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
         <v>82</v>
       </c>
@@ -2401,7 +2193,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
         <v>90</v>
       </c>
@@ -2437,7 +2229,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
         <v>95</v>
       </c>
@@ -2475,7 +2267,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
         <v>103</v>
       </c>
@@ -2513,7 +2305,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
         <v>107</v>
       </c>
@@ -2551,7 +2343,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
         <v>111</v>
       </c>
@@ -2589,7 +2381,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
@@ -2627,7 +2419,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -2665,7 +2457,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
         <v>132</v>
       </c>
@@ -2703,7 +2495,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:12">
       <c r="A22" s="3" t="s">
         <v>138</v>
       </c>
@@ -2739,7 +2531,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
         <v>144</v>
       </c>
@@ -2775,7 +2567,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:12">
       <c r="A24" s="3" t="s">
         <v>79</v>
       </c>
@@ -2811,7 +2603,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
         <v>150</v>
       </c>
@@ -2847,7 +2639,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:12">
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
@@ -2883,7 +2675,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:12">
       <c r="A27" s="3" t="s">
         <v>156</v>
       </c>
@@ -2919,7 +2711,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
         <v>158</v>
       </c>
@@ -2957,7 +2749,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
         <v>164</v>
       </c>
@@ -2995,7 +2787,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:12">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -3031,7 +2823,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:12">
       <c r="A31" s="3" t="s">
         <v>175</v>
       </c>
@@ -3067,7 +2859,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:12">
       <c r="A32" s="3" t="s">
         <v>178</v>
       </c>
@@ -3103,7 +2895,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
         <v>173</v>
       </c>
@@ -3139,7 +2931,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:12">
       <c r="A34" s="3" t="s">
         <v>175</v>
       </c>
@@ -3175,7 +2967,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:12">
       <c r="A35" s="3" t="s">
         <v>79</v>
       </c>
@@ -3211,7 +3003,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:12">
       <c r="A36" s="3" t="s">
         <v>189</v>
       </c>
@@ -3247,7 +3039,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:12">
       <c r="A37" s="3" t="s">
         <v>192</v>
       </c>
@@ -3283,7 +3075,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:12">
       <c r="A38" s="3" t="s">
         <v>149</v>
       </c>
@@ -3319,7 +3111,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:12">
       <c r="A39" s="3" t="s">
         <v>72</v>
       </c>
@@ -3355,7 +3147,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:12">
       <c r="A40" s="3" t="s">
         <v>202</v>
       </c>
@@ -3391,7 +3183,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:12">
       <c r="A41" s="3" t="s">
         <v>205</v>
       </c>
@@ -3427,7 +3219,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:12">
       <c r="A42" s="3" t="s">
         <v>208</v>
       </c>
@@ -3463,7 +3255,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:12">
       <c r="A43" s="3" t="s">
         <v>211</v>
       </c>
@@ -3499,7 +3291,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:12">
       <c r="A44" s="3" t="s">
         <v>208</v>
       </c>
@@ -3535,7 +3327,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:12">
       <c r="A45" s="3" t="s">
         <v>156</v>
       </c>
@@ -3571,7 +3363,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:12">
       <c r="A46" s="3" t="s">
         <v>218</v>
       </c>
@@ -3607,7 +3399,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:12">
       <c r="A47" s="3" t="s">
         <v>221</v>
       </c>
@@ -3643,7 +3435,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:12">
       <c r="A48" s="3" t="s">
         <v>192</v>
       </c>
@@ -3679,7 +3471,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:12">
       <c r="A49" s="3" t="s">
         <v>156</v>
       </c>
@@ -3715,7 +3507,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:12">
       <c r="A50" s="3" t="s">
         <v>222</v>
       </c>
@@ -3751,7 +3543,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:12">
       <c r="A51" s="3" t="s">
         <v>230</v>
       </c>
@@ -3787,7 +3579,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:12">
       <c r="A52" s="3" t="s">
         <v>233</v>
       </c>
@@ -3823,7 +3615,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:12">
       <c r="A53" s="3" t="s">
         <v>236</v>
       </c>
@@ -3859,7 +3651,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:12">
       <c r="A54" s="3" t="s">
         <v>238</v>
       </c>
@@ -3895,7 +3687,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:12">
       <c r="A55" s="2" t="s">
         <v>241</v>
       </c>
@@ -3933,7 +3725,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:12">
       <c r="A56" s="2" t="s">
         <v>247</v>
       </c>
@@ -3971,7 +3763,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:12">
       <c r="A57" s="2" t="s">
         <v>255</v>
       </c>
@@ -4007,7 +3799,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:12">
       <c r="A58" s="2" t="s">
         <v>263</v>
       </c>
@@ -4043,7 +3835,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:12">
       <c r="A59" s="2" t="s">
         <v>266</v>
       </c>
@@ -4079,7 +3871,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:12">
       <c r="A60" s="3" t="s">
         <v>267</v>
       </c>
@@ -4115,7 +3907,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:12">
       <c r="A61" s="3" t="s">
         <v>270</v>
       </c>
@@ -4151,7 +3943,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:12">
       <c r="A62" s="3" t="s">
         <v>273</v>
       </c>
@@ -4187,7 +3979,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:12">
       <c r="A63" s="3" t="s">
         <v>275</v>
       </c>
@@ -4223,7 +4015,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:12">
       <c r="A64" s="3" t="s">
         <v>278</v>
       </c>
@@ -4257,7 +4049,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:12">
       <c r="A65" s="2" t="s">
         <v>280</v>
       </c>
@@ -4293,7 +4085,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:12">
       <c r="A66" s="3" t="s">
         <v>260</v>
       </c>
@@ -4329,7 +4121,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:12">
       <c r="A67" s="2" t="s">
         <v>288</v>
       </c>
@@ -4367,7 +4159,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:12">
       <c r="A68" s="2" t="s">
         <v>286</v>
       </c>
@@ -4405,7 +4197,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:12">
       <c r="A69" s="2" t="s">
         <v>297</v>
       </c>
@@ -4443,7 +4235,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:12">
       <c r="A70" s="2" t="s">
         <v>305</v>
       </c>
@@ -4481,7 +4273,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:12">
       <c r="A71" s="2" t="s">
         <v>311</v>
       </c>
@@ -4519,7 +4311,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:12">
       <c r="A72" s="2" t="s">
         <v>315</v>
       </c>
@@ -4557,7 +4349,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:12">
       <c r="A73" s="2" t="s">
         <v>319</v>
       </c>
@@ -4595,7 +4387,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:12">
       <c r="A74" s="2" t="s">
         <v>323</v>
       </c>
@@ -4633,7 +4425,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:12">
       <c r="A75" s="2" t="s">
         <v>327</v>
       </c>
@@ -4671,7 +4463,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:12">
       <c r="A76" s="2" t="s">
         <v>331</v>
       </c>
@@ -4709,7 +4501,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:12">
       <c r="A77" s="2" t="s">
         <v>337</v>
       </c>
@@ -4747,7 +4539,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:12">
       <c r="A78" s="2" t="s">
         <v>343</v>
       </c>
@@ -4783,7 +4575,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:12">
       <c r="A79" s="3" t="s">
         <v>79</v>
       </c>
@@ -4819,7 +4611,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:12">
       <c r="A80" s="2" t="s">
         <v>353</v>
       </c>
@@ -4855,7 +4647,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:12">
       <c r="A81" s="3" t="s">
         <v>356</v>
       </c>
@@ -4891,7 +4683,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:12">
       <c r="A82" s="3" t="s">
         <v>359</v>
       </c>
@@ -4927,7 +4719,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:12">
       <c r="A83" s="2" t="s">
         <v>362</v>
       </c>
@@ -4963,7 +4755,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:12">
       <c r="A84" s="3" t="s">
         <v>189</v>
       </c>
@@ -4999,7 +4791,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:12">
       <c r="A85" s="3" t="s">
         <v>367</v>
       </c>
@@ -5035,7 +4827,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:12">
       <c r="A86" s="2" t="s">
         <v>370</v>
       </c>
@@ -5071,7 +4863,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:12">
       <c r="A87" s="2" t="s">
         <v>348</v>
       </c>
@@ -5110,629 +4902,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H86">
-    <sortState ref="A2:H86">
-      <sortCondition ref="A2:A86" customList=""/>
+  <autoFilter ref="A1:H86" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H86">
+      <sortCondition ref="A2:A86"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H19" r:id="rId1" display="jongkhom.c@chhindustry.com"/>
-    <hyperlink ref="H55" r:id="rId2" display="somporn20021970@gmail.com"/>
-    <hyperlink ref="H67" r:id="rId3" display="moment.ta.2409@gmail.com"/>
+    <hyperlink ref="H19" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H55" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H67" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14" t="n">
-        <f aca="false">SUM(D2:D33)</f>
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>